--- a/medford_mikrokonveksnye_datchiki_uzi.xlsx
+++ b/medford_mikrokonveksnye_datchiki_uzi.xlsx
@@ -2148,7 +2148,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Микроконвексные датчики УЗИ для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов SonoScape, Siemens, Canon, Mindray, Samsung, GE, Edan — всего 20 позиций.</t>
+          <t>Микроконвексные датчики УЗИ для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов SonoScape, Siemens, Canon, Mindray, Samsung, GE, Edan.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">

--- a/medford_mikrokonveksnye_datchiki_uzi.xlsx
+++ b/medford_mikrokonveksnye_datchiki_uzi.xlsx
@@ -941,7 +941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1022,12 +1022,12 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать микроконвексные датчики УЗИ для клиники?</t>
+          <t>Чем микроконвексный датчик отличается от конвексного?</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Выбор зависит от задач отделения, совместимости с оборудованием и ключевых характеристик (Диапазон частот, МГц, Количество элементов, Радиус кривизны, мм, Размер апертуры, мм). Учитывайте бренд, гарантию, сервис и наличие РУ. Поможем сравнить модели и подобрать оптимальную.</t>
+          <t>Микроконвексный датчик — уменьшенная и сильно изогнутая версия конвексного, с малым радиусом кривизны (в каталоге 10–40 мм). Он даёт компактное пятно контакта и широкий веерообразный обзор из узкого акустического окна. Обычный конвексный крупнее и глубже проникает, поэтому его чаще применяют для абдоминальных исследований у взрослых.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -1060,12 +1060,12 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Нужно ли регистрационное удостоверение (РУ)?</t>
+          <t>Для каких исследований нужен микроконвексный датчик?</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Да. Это медицинское изделие; для закупки в клинику с медицинской лицензией необходимо действующее регистрационное удостоверение Росздравнадзора. Проверяйте наличие РУ на конкретную модель.</t>
+          <t>Наружные модели применяют в педиатрии и неонатологии (в том числе нейросонография через родничок), при межрёберном сканировании печени и селезёнки и в кардиологии через узкие промежутки. Внутриполостные — в гинекологии, урологии и проктологии. Конкретное исследование и выбор датчика под него определяет врач по клинической задаче.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Какие бренды представлены в каталоге?</t>
+          <t>Как выбрать частоту датчика?</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>В каталоге представлены SonoScape, Siemens, Canon, Mindray, Samsung, GE, Edan. Подберём модель под ваши задачи, совместимость и бюджет.</t>
+          <t>Частота определяет баланс разрешения и глубины: высокие частоты дают детальное изображение, но проникают на 10–15 см, низкие достают глубже с меньшей детализацией. В каталоге диапазон — 2,0–12,8 МГц, есть широкополосные модели. Частоту согласуют с глубиной исследуемых структур; для поверхностных и глубоких задач акценты различаются.</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -1136,12 +1136,12 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Сколько стоит оборудование?</t>
+          <t>Что означает радиус кривизны?</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Цена указывается по запросу и зависит от модели, комплектации и условий поставки. Отправьте запрос — подготовим коммерческое предложение за 1 день.</t>
+          <t>Радиус кривизны — степень изогнутости рабочей поверхности датчика. Малый радиус (10–11 мм) даёт компактное пятно контакта и широкий обзор из узкого окна, удобен для внутриполостных и детских исследований. Больший радиус (до 40 мм) ближе к обычному конвексному датчику. В каталоге радиус кривизны моделей — от 10 до 40 мм.</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1174,12 +1174,12 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Есть ли гарантия, сервис и обучение?</t>
+          <t>Подойдёт ли датчик к моему аппарату УЗИ?</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Да. Обеспечиваем доставку по России, монтаж и ввод в эксплуатацию, обучение персонала, гарантийное и постгарантийное обслуживание, поставку расходных материалов. Телефон: +7 (499) 495-48-21.</t>
+          <t>Датчик совместим только со своим сканером и разъёмом платформы: преобразователь Mindray работает со сканерами Mindray, Siemens — с Siemens и так далее. Универсальной совместимости между марками нет. Перед покупкой сверяют модель аппарата со списком поддерживаемых датчиков в документации производителя, иначе датчик не заведётся.</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1212,12 +1212,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Что такое конвексный датчик УЗИ?</t>
+          <t>Как обрабатывают внутриполостные датчики?</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Зависит от модели и клинической задачи. Подберём вариант под ваши требования и ответим на вопрос при консультации — напишите или позвоните: +7 (499) 495-48-21.</t>
+          <t>Внутриполостные датчики применяют с одноразовыми защитными чехлами и подвергают дезинфекции согласно инструкции производителя. Строгое соблюдение обработки — обязательное требование санитарной безопасности. Совместимость с чехлами и допустимые дезинфицирующие средства уточняют по документации модели, поскольку не все средства подходят для акустической поверхности датчика.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1250,12 +1250,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Какие существуют типы датчиков для УЗИ?</t>
+          <t>Сколько элементов должно быть у датчика?</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Зависит от модели и клинической задачи. Подберём вариант под ваши требования и ответим на вопрос при консультации — напишите или позвоните: +7 (499) 495-48-21.</t>
+          <t>Число элементов у моделей каталога — от 80 до 192. Больше элементов при прочих равных даёт более плотную линию сканирования и потенциально лучшую детализацию. Однако итоговое качество зависит от связки датчика, частоты и возможностей сканера, поэтому число элементов оценивают вместе с остальными параметрами, а не отдельно.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -1264,6 +1264,44 @@
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>FAQ_08</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Нужно ли регистрационное удостоверение?</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Да. Датчик УЗИ — медицинское изделие, вводимое в оборот при действующем регистрационном удостоверении Росздравнадзора на модель. Перед приобретением сверяют статус РУ, совместимость со сканером, а для внутриполостных моделей — режим обработки и совместимость с защитными чехлами, а также условия сервиса у поставщика.</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>mikrokonveksnye_datchiki_uzi</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>FAQ</t>
         </is>
@@ -2148,7 +2186,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Микроконвексные датчики УЗИ для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов SonoScape, Siemens, Canon, Mindray, Samsung, GE, Edan.</t>
+          <t>Микроконвексный датчик УЗИ — уменьшенная и сильно изогнутая версия конвексного преобразователя с малым радиусом кривизны, компактным пятном контакта и широким веерообразным обзором. В каталоге собраны модели Mindray, Siemens, Canon, Samsung, GE, SonoScape, Edan, SIUI и Chison с частотным диапазоном от 2,0 до 12,8 МГц и радиусом кривизны от 10 до 40 мм. Число элементов у моделей — от 80 до 192. Представлены как внутриполостные датчики (Mindray V11-3HB, Siemens EC9-4, SonoScape 6V3), так и наружные для педиатрии и межрёберного сканирования.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -2432,7 +2470,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Сравнение моделей по характеристикам</t>
+          <t>Типы микроконвексных датчиков</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr"/>
@@ -2720,7 +2758,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Что такое микроконвексные датчики УЗИ</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr"/>
@@ -4520,247 +4558,75 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>04_COMPARE_ROWS — Сравнение моделей по характеристикам</t>
+          <t>04_COMPARE_ROWS — Типы микроконвексных датчиков</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Модель</t>
+          <t>Тип</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Бренд</t>
+          <t>Применение</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Диапазон частот, МГц</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Количество элементов</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Радиус кривизны, мм</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Размер апертуры, мм</t>
+          <t>Примеры</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Вагинально-ректальный датчик SonoScape 6V3</t>
+          <t>Наружные (поверхностные)</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>SonoScape</t>
+          <t>педиатрия, неонатология, межрёберное сканирование, кардиология</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>4.0–11.0</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>Canon PVT-674BT, GE RNA5-9-D, SIUI C6LN</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Siemens EV-8C4 микроконвексный внутриполостной датчик УЗИ</t>
+          <t>Внутриполостные</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Siemens</t>
+          <t>гинекология, урология, проктология</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>4-9</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Siemens EC9-4 микроконвексный внутриполостной датчик УЗИ</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Siemens</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>3,6-8</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Микроконвексный датчик Canon PVT-674BT</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Canon</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>3,5-9,7</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Микроконвексный внутриполостной датчик Mindray V11-3BE</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Mindray</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>2.6-12.8</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>12,06</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>SIUI C3I20C микроконвексный внутриполостной датчик</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr"/>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>2,0-5,0</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Mindray V11-3HB, Siemens EC9-4, SonoScape 6V3</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4772,7 +4638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -5098,12 +4964,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Тип и назначение</t>
+          <t>Проверьте совместимость со сканером</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Определите задачи, под которые подбирается микроконвексные датчики УЗИ: профиль отделения, поток и характер исследований или процедур.</t>
+          <t>Датчик работает только со своим УЗ-сканером и разъёмом платформы. Сначала уточняют марку и модель аппарата и список поддерживаемых им датчиков: преобразователь Mindray рассчитан на сканеры Mindray, Siemens — на Siemens и так далее. Совместимость первична; частота и радиус кривизны имеют смысл только для подходящего аппарата.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -5143,12 +5009,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Совместимость с оборудованием</t>
+          <t>Выберите частоту под глубину</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Проверьте совместимость с имеющейся техникой, платформой и разъёмами — это исключит лишние затраты на дооснащение.</t>
+          <t>Частотный диапазон моделей каталога — 2,0–12,8 МГц. Высокие частоты дают лучшее разрешение, но ограничивают глубину проникновения до 10–15 см; низкие достают глубже с меньшей детализацией. Широкополосные датчики (Mindray V11-3BE 2,6–12,8 МГц) охватывают широкий диапазон. Частоту согласуют с глубиной исследуемых структур и профилем пациентов.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr"/>
@@ -5188,12 +5054,12 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Ключевые характеристики</t>
+          <t>Оцените радиус кривизны</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Сравните ключевые параметры моделей: Диапазон частот, МГц, Количество элементов, Радиус кривизны, мм, Размер апертуры, мм. Значения — в таблице сравнения и карточках товаров.</t>
+          <t>Радиус кривизны у моделей — от 10 до 40 мм. Малый радиус (Edan MC9-3TQ — 10 мм, Mindray V11-3s — 11 мм) даёт компактное пятно контакта и широкий обзор из узкого окна, удобен для внутриполостных и педиатрических исследований. Больший радиус (Canon PVT-674BT — 40 мм) ближе к обычному конвексному. Радиус подбирают под зону доступа.</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
@@ -5233,12 +5099,12 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Бренд и качество</t>
+          <t>Определите тип: наружный или внутриполостной</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Выбор бренда влияет на ресурс, сервис и совместимость. В каталоге: SonoScape, Siemens, Canon, Mindray, Samsung, GE, Edan.</t>
+          <t>Наружные (поверхностные) датчики применяют для трансабдоминальных исследований у детей, неонатологии, межрёберного сканирования и кардиологии. Внутриполостные (трансвагинальные, трансректальные) — для гинекологии, урологии и проктологии. В каталоге есть оба типа. Назначение датчика определяет форму корпуса и требования к обработке; выбор под исследование определяет врач.</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
@@ -5278,12 +5144,12 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Регистрация и допуск</t>
+          <t>Учтите число элементов</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Для клиники с медицинской лицензией необходимо действующее регистрационное удостоверение (РУ) Росздравнадзора на модель.</t>
+          <t>Число элементов у моделей каталога — от 80 до 192 (Edan C611-2 — 80, SonoScape 6V3 и Samsung EA2-11B — 192). Больше элементов при прочих равных даёт более плотную линию сканирования и потенциально лучшую детализацию изображения. Значение параметра оценивают в связке с частотой, радиусом кривизны и возможностями самого сканера.</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
@@ -5323,12 +5189,12 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Гарантия и сервис</t>
+          <t>Уточните обработку и регистрацию</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте гарантию, наличие сервисной поддержки и поставку расходных материалов до закупки.</t>
+          <t>Для внутриполостных датчиков проверяют совместимость с одноразовыми защитными чехлами и допустимый режим дезинфекции — это обязательное требование санитарной безопасности. Перед вводом в оборот сверяют действующее регистрационное удостоверение Росздравнадзора на модель и условия сервисной поддержки. Кабель и разъём датчика относятся к нагруженным узлам и требуют аккуратного обращения.</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr"/>
@@ -5378,7 +5244,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Микроконвексные датчики УЗИ подбирают под задачи отделения и совместимость с имеющимся оборудованием. В нашем каталоге представлены SonoScape, Siemens, Canon, Mindray, Samsung, GE, Edan. При выборе обращают внимание на диапазон частот, количество элементов, радиус кривизны, размер апертуры, а также на наличие регистрационного удостоверения и условия сервиса. Поможем сравнить модели и подобрать оптимальную под ваш поток исследований и бюджет.</t>
+          <t>Датчик выбирают строго под свой сканер — микроконвексный преобразователь от другой платформы просто не заведётся. Дальше смотрю на частотный диапазон: высокие частоты дают детализацию, но ограничивают глубину, поэтому под межрёберное сканирование печени и под неонатологию нужны разные акценты. Радиус кривизны в каталоге от 10 до 40 мм определяет пятно контакта и угол обзора. Для внутриполостных моделей отдельно проверяю совместимость с защитными чехлами и режим дезинфекции.</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -5662,13 +5528,13 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Что такое микроконвексные датчики УЗИ</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Микроконвексные датчики УЗИ — медицинское оборудование для оснащения клиник и медицинских учреждений. В каталоге Medford представлены модели брендов SonoScape, Siemens, Canon, Mindray, Samsung, GE, Edan. Подберём вариант под задачи вашего отделения.</t>
+          <t>Микроконвексный датчик УЗИ — компактный сильно изогнутый преобразователь с малым радиусом кривизны (в каталоге 10–40 мм) и широким веерообразным обзором. Его применяют там, где нужен доступ через узкое акустическое окно: педиатрия, неонатология, межрёберное сканирование, а также внутриполостные исследования. Частотный диапазон моделей — 2,0–12,8 МГц, число элементов — 80–192. Главный критерий выбора — совместимость с конкретным УЗ-сканером. Затем оценивают частоту под глубину, радиус кривизны и тип (наружный или внутриполостной). Выбор под исследование определяет врач.</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -5705,13 +5571,13 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать и на что смотреть</t>
+          <t>Что такое микроконвексный датчик УЗИ</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr"/>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>При выборе оценивают назначение и совместимость с имеющимся оборудованием, ключевые характеристики (Диапазон частот, МГц, Количество элементов, Радиус кривизны, мм, Размер апертуры, мм), бренд, наличие РУ, гарантию и сервис.</t>
+          <t>Микроконвексный датчик — уменьшенный и сильно изогнутый вариант конвексного преобразователя с малым радиусом кривизны. Компактное пятно контакта и широкий веерообразный обзор позволяют работать в условиях ограниченного акустического доступа. Пьезоэлементы расположены по крутой дуге, что обеспечивает широкий угол сканирования при малой площади контакта с телом пациента.</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -5748,13 +5614,13 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Оснащение и совместимость</t>
+          <t>Характеристики и частота</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr"/>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте комплектацию, совместимость с вашей техникой и наличие расходных материалов. Специалисты Medford помогут собрать рабочее решение под ваш профиль.</t>
+          <t>Ключевые параметры — частотный диапазон, радиус кривизны и число элементов. В каталоге частота моделей составляет 2,0–12,8 МГц, радиус кривизны — 10–40 мм, число элементов — 80–192. Высокие частоты дают лучшее разрешение при глубине до 10–15 см, малый радиус кривизны обеспечивает доступ через узкое акустическое окно.</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -5791,13 +5657,13 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Оплата и доставка</t>
+          <t>Виды и применение</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr"/>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Оплата — по счёту для юридических лиц и ИП. Доставка по всей России, монтаж и ввод в эксплуатацию. Гарантийное и постгарантийное обслуживание, обучение персонала. Телефон для консультаций: +7 (499) 495-48-21.</t>
+          <t>Микроконвексные датчики делят на наружные и внутриполостные. Наружные применяют в педиатрии, неонатологии, при межрёберном сканировании и в кардиологии; внутриполостные — в гинекологии, урологии и проктологии. В каталоге представлены обе группы от Mindray, Siemens, Canon, Samsung, GE, SonoScape, Edan и SIUI.</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -5814,6 +5680,49 @@
       <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="inlineStr"/>
       <c r="M24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>SEO_05</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>550</v>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Совместимость и обработка</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Датчик работает только со своим сканером и разъёмом платформы, поэтому совместимость сверяют по документации до покупки. Внутриполостные модели применяют с одноразовыми чехлами и дезинфицируют по инструкции. Перед вводом в оборот проверяют регистрационное удостоверение Росздравнадзора и условия сервиса; кабель и разъём датчика требуют аккуратного обращения.</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>mikrokonveksnye_datchiki_uzi</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr"/>
+      <c r="L25" s="3" t="inlineStr"/>
+      <c r="M25" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
